--- a/diseases/d124/2000-2004.xlsx
+++ b/diseases/d124/2000-2004.xlsx
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18069,7 +18069,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -30732,7 +30732,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -33186,7 +33186,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -34413,7 +34413,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -35640,7 +35640,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -36867,7 +36867,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -38094,7 +38094,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -39321,7 +39321,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -40548,7 +40548,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -41775,7 +41775,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -43002,7 +43002,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -44229,7 +44229,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -45849,7 +45849,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -47224,7 +47224,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -48599,7 +48599,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -49974,7 +49974,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -51349,7 +51349,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -52724,7 +52724,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -54099,7 +54099,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -55326,7 +55326,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -56701,7 +56701,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -58076,7 +58076,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -59451,7 +59451,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -60826,7 +60826,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -62594,7 +62594,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -63969,7 +63969,7 @@
       </c>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN361" t="b">
@@ -65344,7 +65344,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -66719,7 +66719,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -68094,7 +68094,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -69469,7 +69469,7 @@
       </c>
       <c r="AM393" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN393" t="b">
@@ -70844,7 +70844,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -72219,7 +72219,7 @@
       </c>
       <c r="AM409" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN409" t="b">
@@ -73594,7 +73594,7 @@
       </c>
       <c r="AM417" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN417" t="b">
@@ -74969,7 +74969,7 @@
       </c>
       <c r="AM425" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN425" t="b">
@@ -76344,7 +76344,7 @@
       </c>
       <c r="AM433" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN433" t="b">
@@ -77719,7 +77719,7 @@
       </c>
       <c r="AM441" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN441" t="b">
